--- a/Heat_Treatment_4140.xlsx
+++ b/Heat_Treatment_4140.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahsa\mu_code\Metallurgy_Ai_Projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahsa\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="8">
   <si>
     <t>Aust_Temp (°C)</t>
   </si>
@@ -41,7 +41,13 @@
     <t>Hardness (HRC)</t>
   </si>
   <si>
-    <t>2 (روغن)</t>
+    <t>2(Oil)</t>
+  </si>
+  <si>
+    <t>1(Water)</t>
+  </si>
+  <si>
+    <t>3(Brine)</t>
   </si>
 </sst>
 </file>
@@ -71,7 +77,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -94,11 +100,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -107,6 +124,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -389,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
@@ -434,13 +455,13 @@
         <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="3">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="D3" s="4">
+        <v>200</v>
       </c>
       <c r="E3" s="3">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -451,13 +472,13 @@
         <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="3">
-        <v>400</v>
+        <v>7</v>
+      </c>
+      <c r="D4" s="4">
+        <v>200</v>
       </c>
       <c r="E4" s="3">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -471,10 +492,10 @@
         <v>5</v>
       </c>
       <c r="D5" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E5" s="3">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -485,13 +506,183 @@
         <v>60</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3">
+        <v>300</v>
+      </c>
+      <c r="E6" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>850</v>
+      </c>
+      <c r="B7" s="3">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>300</v>
+      </c>
+      <c r="E7" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>850</v>
+      </c>
+      <c r="B8" s="3">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>850</v>
+      </c>
+      <c r="B9" s="3">
+        <v>60</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>850</v>
+      </c>
+      <c r="B10" s="3">
+        <v>60</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>850</v>
+      </c>
+      <c r="B11" s="3">
+        <v>60</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="3">
+        <v>500</v>
+      </c>
+      <c r="E11" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>850</v>
+      </c>
+      <c r="B12" s="3">
+        <v>60</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>850</v>
+      </c>
+      <c r="B13" s="3">
+        <v>60</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3">
+        <v>500</v>
+      </c>
+      <c r="E13" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>850</v>
+      </c>
+      <c r="B14" s="3">
+        <v>60</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="3">
         <v>600</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E14" s="3">
         <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>850</v>
+      </c>
+      <c r="B15" s="3">
+        <v>60</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>850</v>
+      </c>
+      <c r="B16" s="3">
+        <v>60</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3">
+        <v>600</v>
+      </c>
+      <c r="E16" s="5">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
